--- a/Extracted_data_analysis/tropical/Output-Transformed_data/geographical_distribution_summary.xlsx
+++ b/Extracted_data_analysis/tropical/Output-Transformed_data/geographical_distribution_summary.xlsx
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>84</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="B25">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="B29">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30">
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="B32">
-        <v>231</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="B33">
-        <v>139</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -940,7 +940,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -967,10 +967,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>70</v>
+        <v>412</v>
       </c>
       <c r="C2">
-        <v>16</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3">
@@ -980,10 +980,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>298</v>
+        <v>28</v>
       </c>
       <c r="C3">
-        <v>67</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -993,74 +993,22 @@
         </is>
       </c>
       <c r="B4">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="C4">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>8</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>4</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9">
         <v>0</v>
       </c>
     </row>
